--- a/extracted_cycles.xlsx
+++ b/extracted_cycles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.18e+03</t>
+          <t>1.44e+03</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.18e+04</t>
+          <t>3.76e+00</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.58e+03</t>
+          <t>1.48e+02</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.31e+04</t>
+          <t>4.57e+01</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.32e+04</t>
+          <t>4.85e+01</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.19e+04</t>
+          <t>1.55e+02</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.20e+04</t>
+          <t>1.62e+02</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.53e+04</t>
+          <t>3.69e+01</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.10e+04</t>
+          <t>1.60e+02</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.34e+04</t>
+          <t>3.83e+01</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.15e+04</t>
+          <t>1.45e+02</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.42e+04</t>
+          <t>1.34e+02</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.66e+04</t>
+          <t>1.77e+02</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.46e+06</t>
+          <t>3.73e+01</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6.25e+04</t>
+          <t>1.55e+02</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,103 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3.88e+03</t>
+          <t>3.80e+01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>layer-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.69e+02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>layer-17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.42e+02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>layer-18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.83e+02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>layer-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5.70e+01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>layer-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2.30e+02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>layer-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5.74e+01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>layer-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.79e+02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>layer-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3.83e+01</t>
         </is>
       </c>
     </row>
